--- a/ukol_2/programy/Excel/Program_excel.xlsx
+++ b/ukol_2/programy/Excel/Program_excel.xlsx
@@ -1,25 +1,139 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mapri\Documents\SOP\SOP-2026-A\ukol_2\programy\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E538C118-5C6F-4B58-A308-907483F58A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">List1!$D$10:$E$10</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">List1!$F$12</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">List1!$F$13</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">List1!$F$14</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">List1!$F$15</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">4</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">List1!$F$16</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">List1!$F$4</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">List1!$F$5</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">List1!$F$6</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">List1!$F$7</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>Skleněné</t>
+  </si>
+  <si>
+    <t>Dřevěné</t>
+  </si>
+  <si>
+    <t>Počet noh</t>
+  </si>
+  <si>
+    <t>Dřevěná deska</t>
+  </si>
+  <si>
+    <t>Skleněná deska</t>
+  </si>
+  <si>
+    <t>Sklad</t>
+  </si>
+  <si>
+    <t>Čas</t>
+  </si>
+  <si>
+    <t>Prodejní cena</t>
+  </si>
+  <si>
+    <t>Počet kusů</t>
+  </si>
+  <si>
+    <t>Zisk</t>
+  </si>
+  <si>
+    <t>Celkový počet noh</t>
+  </si>
+  <si>
+    <t>Celkový počet dřevěných desek</t>
+  </si>
+  <si>
+    <t>Celkový počet skleněných desek</t>
+  </si>
+  <si>
+    <t>Celkový čas</t>
+  </si>
+  <si>
+    <t>Vstupní hodnoty</t>
+  </si>
+  <si>
+    <t>Proměnné</t>
+  </si>
+  <si>
+    <t>Součty</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -29,15 +143,33 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +177,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +501,239 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="1"/>
+      <c r="C4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5">
+        <v>5</v>
+      </c>
+      <c r="F4" s="5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="1"/>
+      <c r="C5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="1"/>
+      <c r="C6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="1"/>
+      <c r="C7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="F7" s="7">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="1"/>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="5">
+        <v>200</v>
+      </c>
+      <c r="E8" s="5">
+        <v>350</v>
+      </c>
+      <c r="F8" s="5"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="1"/>
+      <c r="C10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5">
+        <v>30.000000150936849</v>
+      </c>
+      <c r="E10" s="5">
+        <v>29.999999849063151</v>
+      </c>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="C12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="5">
+        <f>D10*D4</f>
+        <v>150.00000075468424</v>
+      </c>
+      <c r="E12" s="5">
+        <f>E10*E4</f>
+        <v>149.99999924531576</v>
+      </c>
+      <c r="F12" s="5">
+        <f>SUM(D12:E12)</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="7">
+        <f>D10*D5</f>
+        <v>30.000000150936849</v>
+      </c>
+      <c r="E13" s="7">
+        <f>E10*E5</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" ref="F13:F15" si="0">SUM(D13:E13)</f>
+        <v>30.000000150936849</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5">
+        <f>D10*D6</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <f>E10*E6</f>
+        <v>29.999999849063151</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="0"/>
+        <v>29.999999849063151</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="7">
+        <f>D10*D7</f>
+        <v>18.000000090562107</v>
+      </c>
+      <c r="E15" s="7">
+        <f>E10*E7</f>
+        <v>44.999999773594723</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="0"/>
+        <v>62.999999864156834</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+      <c r="C16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5">
+        <f>D10*D8</f>
+        <v>6000.0000301873697</v>
+      </c>
+      <c r="E16" s="5">
+        <f>E10*E8</f>
+        <v>10499.999947172102</v>
+      </c>
+      <c r="F16" s="5">
+        <f>SUM(D16:E16)</f>
+        <v>16499.999977359472</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ukol_2/programy/Excel/Program_excel.xlsx
+++ b/ukol_2/programy/Excel/Program_excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mapri\Documents\SOP\SOP-2026-A\ukol_2\programy\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vutbr-my.sharepoint.com/personal/257575_vutbr_cz/Documents/Bc-3_2/SOP/SOP-2026-A/ukol_2/programy/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E538C118-5C6F-4B58-A308-907483F58A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{E538C118-5C6F-4B58-A308-907483F58A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A60BF62-946D-4371-8CC7-9B4056711F21}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -196,12 +196,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -516,23 +513,23 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="2"/>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="1"/>
@@ -541,194 +538,194 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>5</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>5</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>300</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>0</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>1</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>0.6</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>1.5</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>200</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>350</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="4"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="2"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>30.000000150936849</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>29.999999849063151</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="4"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="2"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <f>D10*D4</f>
         <v>150.00000075468424</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f>E10*E4</f>
         <v>149.99999924531576</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <f>SUM(D12:E12)</f>
         <v>300</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <f>D10*D5</f>
         <v>30.000000150936849</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <f>E10*E5</f>
         <v>0</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <f t="shared" ref="F13:F15" si="0">SUM(D13:E13)</f>
         <v>30.000000150936849</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <f>D10*D6</f>
         <v>0</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f>E10*E6</f>
         <v>29.999999849063151</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <f t="shared" si="0"/>
         <v>29.999999849063151</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="1"/>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <f>D10*D7</f>
         <v>18.000000090562107</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <f>E10*E7</f>
         <v>44.999999773594723</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
         <v>62.999999864156834</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <f>D10*D8</f>
         <v>6000.0000301873697</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f>E10*E8</f>
         <v>10499.999947172102</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <f>SUM(D16:E16)</f>
         <v>16499.999977359472</v>
       </c>

--- a/ukol_2/programy/Excel/Program_excel.xlsx
+++ b/ukol_2/programy/Excel/Program_excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vutbr-my.sharepoint.com/personal/257575_vutbr_cz/Documents/Bc-3_2/SOP/SOP-2026-A/ukol_2/programy/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{E538C118-5C6F-4B58-A308-907483F58A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A60BF62-946D-4371-8CC7-9B4056711F21}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="13_ncr:1_{E538C118-5C6F-4B58-A308-907483F58A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7D1BB9C-2B11-41F4-ADA2-22688FE7A730}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="1185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -234,6 +234,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
